--- a/uloha7/uloha7.xlsx
+++ b/uloha7/uloha7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE91630-FA51-4C4D-8A86-60488610D3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697A9A5B-5ECD-4822-A82F-4A84E72CC8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C78186FA-06F9-4A36-99E9-9DBABD2AC56F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>kondenzator</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>C</t>
-  </si>
-  <si>
-    <t>R_A (ohm)</t>
   </si>
   <si>
     <t>F</t>
@@ -108,6 +105,12 @@
   </si>
   <si>
     <t>L (mH)</t>
+  </si>
+  <si>
+    <t>nejistota</t>
+  </si>
+  <si>
+    <t>R_A (Mohm)</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1124,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="cs-CZ"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5070,7 +5073,7 @@
         <v>6</v>
       </c>
       <c r="J1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -5111,33 +5114,57 @@
         <v>5</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10.34</v>
       </c>
+      <c r="B3">
+        <f>0.01*A3+0.03</f>
+        <v>0.13340000000000002</v>
+      </c>
       <c r="C3">
         <v>2.15</v>
       </c>
+      <c r="D3">
+        <f>0.015*C3+0.03</f>
+        <v>6.225E-2</v>
+      </c>
       <c r="E3">
         <v>10.33</v>
       </c>
+      <c r="F3">
+        <f>0.01*E3+0.03</f>
+        <v>0.1333</v>
+      </c>
       <c r="G3">
         <v>4.4800000000000004</v>
       </c>
+      <c r="H3">
+        <f>0.015*G3+0.03</f>
+        <v>9.7200000000000009E-2</v>
+      </c>
       <c r="J3">
         <v>1.288</v>
       </c>
+      <c r="K3">
+        <f>0.01*J3+0.003</f>
+        <v>1.5880000000000002E-2</v>
+      </c>
       <c r="L3">
         <v>255.6</v>
       </c>
+      <c r="M3">
+        <f>0.015*L3+0.3</f>
+        <v>4.1339999999999995</v>
+      </c>
       <c r="N3">
-        <f>SQRT((J3/L3*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" ref="N3:N12" si="0">SQRT((J3/L3*1000)^2-$K$45^2)/$G$35*1000</f>
         <v>13.500589896054429</v>
       </c>
     </row>
@@ -5145,23 +5172,47 @@
       <c r="A4">
         <v>8.51</v>
       </c>
+      <c r="B4">
+        <f t="shared" ref="B4:B8" si="1">0.01*A4+0.03</f>
+        <v>0.11509999999999999</v>
+      </c>
       <c r="C4">
         <v>1.75</v>
       </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D8" si="2">0.015*C4+0.03</f>
+        <v>5.6249999999999994E-2</v>
+      </c>
       <c r="E4">
         <v>8.4499999999999993</v>
       </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F6" si="3">0.01*E4+0.03</f>
+        <v>0.11449999999999999</v>
+      </c>
       <c r="G4">
         <v>3.62</v>
       </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H8" si="4">0.015*G4+0.03</f>
+        <v>8.43E-2</v>
+      </c>
       <c r="J4">
         <v>1.111</v>
       </c>
+      <c r="K4">
+        <f t="shared" ref="K4:K12" si="5">0.01*J4+0.003</f>
+        <v>1.4110000000000001E-2</v>
+      </c>
       <c r="L4">
         <v>220.8</v>
       </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M10" si="6">0.015*L4+0.3</f>
+        <v>3.6119999999999997</v>
+      </c>
       <c r="N4">
-        <f>SQRT((J4/L4*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.472517392499672</v>
       </c>
     </row>
@@ -5169,23 +5220,47 @@
       <c r="A5">
         <v>7.09</v>
       </c>
+      <c r="B5">
+        <f t="shared" si="1"/>
+        <v>0.1009</v>
+      </c>
       <c r="C5">
         <v>1.43</v>
       </c>
+      <c r="D5">
+        <f t="shared" si="2"/>
+        <v>5.1449999999999996E-2</v>
+      </c>
       <c r="E5">
         <v>6.99</v>
       </c>
+      <c r="F5">
+        <f t="shared" si="3"/>
+        <v>9.9900000000000003E-2</v>
+      </c>
       <c r="G5">
         <v>2.96</v>
       </c>
+      <c r="H5">
+        <f t="shared" si="4"/>
+        <v>7.4399999999999994E-2</v>
+      </c>
       <c r="J5">
         <v>1.018</v>
       </c>
+      <c r="K5">
+        <f t="shared" si="5"/>
+        <v>1.3180000000000001E-2</v>
+      </c>
       <c r="L5">
         <v>202.3</v>
       </c>
+      <c r="M5">
+        <f t="shared" si="6"/>
+        <v>3.3344999999999998</v>
+      </c>
       <c r="N5">
-        <f>SQRT((J5/L5*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.474135462411144</v>
       </c>
     </row>
@@ -5193,23 +5268,47 @@
       <c r="A6">
         <v>5.64</v>
       </c>
+      <c r="B6">
+        <f t="shared" si="1"/>
+        <v>8.6400000000000005E-2</v>
+      </c>
       <c r="C6">
         <v>1.1399999999999999</v>
       </c>
+      <c r="D6">
+        <f t="shared" si="2"/>
+        <v>4.7099999999999996E-2</v>
+      </c>
       <c r="E6">
         <v>5.41</v>
       </c>
+      <c r="F6">
+        <f t="shared" si="3"/>
+        <v>8.4100000000000008E-2</v>
+      </c>
       <c r="G6">
         <v>2.27</v>
       </c>
+      <c r="H6">
+        <f t="shared" si="4"/>
+        <v>6.4049999999999996E-2</v>
+      </c>
       <c r="J6">
         <v>0.875</v>
       </c>
+      <c r="K6">
+        <f t="shared" si="5"/>
+        <v>1.175E-2</v>
+      </c>
       <c r="L6">
         <v>173.7</v>
       </c>
+      <c r="M6">
+        <f t="shared" si="6"/>
+        <v>2.9054999999999995</v>
+      </c>
       <c r="N6">
-        <f>SQRT((J6/L6*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.494149777452796</v>
       </c>
     </row>
@@ -5217,23 +5316,47 @@
       <c r="A7">
         <v>3.6219999999999999</v>
       </c>
+      <c r="B7">
+        <f>0.01*A7+0.003</f>
+        <v>3.9220000000000005E-2</v>
+      </c>
       <c r="C7">
         <v>0.73</v>
       </c>
+      <c r="D7">
+        <f t="shared" si="2"/>
+        <v>4.095E-2</v>
+      </c>
       <c r="E7">
         <v>3.5230000000000001</v>
       </c>
+      <c r="F7">
+        <f>0.01*E7+0.003</f>
+        <v>3.8230000000000007E-2</v>
+      </c>
       <c r="G7">
         <v>1.47</v>
       </c>
+      <c r="H7">
+        <f t="shared" si="4"/>
+        <v>5.2049999999999999E-2</v>
+      </c>
       <c r="J7">
         <v>0.754</v>
       </c>
+      <c r="K7">
+        <f t="shared" si="5"/>
+        <v>1.0540000000000001E-2</v>
+      </c>
       <c r="L7">
         <v>149.80000000000001</v>
       </c>
+      <c r="M7">
+        <f t="shared" si="6"/>
+        <v>2.5469999999999997</v>
+      </c>
       <c r="N7">
-        <f>SQRT((J7/L7*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.478855148477555</v>
       </c>
     </row>
@@ -5241,41 +5364,73 @@
       <c r="A8">
         <v>1.7010000000000001</v>
       </c>
+      <c r="B8">
+        <f>0.01*A8+0.003</f>
+        <v>2.001E-2</v>
+      </c>
       <c r="C8">
         <v>0.34</v>
       </c>
+      <c r="D8">
+        <f t="shared" si="2"/>
+        <v>3.5099999999999999E-2</v>
+      </c>
       <c r="E8">
         <v>1.577</v>
       </c>
+      <c r="F8">
+        <f>0.01*E8+0.003</f>
+        <v>1.8769999999999998E-2</v>
+      </c>
       <c r="G8">
         <v>0.65</v>
       </c>
+      <c r="H8">
+        <f t="shared" si="4"/>
+        <v>3.9750000000000001E-2</v>
+      </c>
       <c r="J8">
         <v>0.63700000000000001</v>
       </c>
+      <c r="K8">
+        <f t="shared" si="5"/>
+        <v>9.3699999999999999E-3</v>
+      </c>
       <c r="L8">
         <v>126.5</v>
       </c>
+      <c r="M8">
+        <f t="shared" si="6"/>
+        <v>2.1974999999999998</v>
+      </c>
       <c r="N8">
-        <f>SQRT((J8/L8*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.487160512850878</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
         <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
       </c>
       <c r="J9">
         <v>0.51100000000000001</v>
       </c>
+      <c r="K9">
+        <f>0.01*J9+0.0003</f>
+        <v>5.4099999999999999E-3</v>
+      </c>
       <c r="L9">
         <v>101.6</v>
       </c>
+      <c r="M9">
+        <f t="shared" si="6"/>
+        <v>1.8239999999999998</v>
+      </c>
       <c r="N9">
-        <f>SQRT((J9/L9*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.464284880753191</v>
       </c>
     </row>
@@ -5307,11 +5462,19 @@
       <c r="J10">
         <v>0.37340000000000001</v>
       </c>
+      <c r="K10">
+        <f>0.01*J10+0.0003</f>
+        <v>4.0340000000000003E-3</v>
+      </c>
       <c r="L10">
         <v>74.099999999999994</v>
       </c>
+      <c r="M10">
+        <f t="shared" si="6"/>
+        <v>1.4115</v>
+      </c>
       <c r="N10">
-        <f>SQRT((J10/L10*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.500637818004645</v>
       </c>
     </row>
@@ -5319,23 +5482,47 @@
       <c r="A11">
         <v>10.119999999999999</v>
       </c>
+      <c r="B11">
+        <f>0.01*A11+0.03</f>
+        <v>0.13119999999999998</v>
+      </c>
       <c r="C11">
         <v>10.28</v>
       </c>
+      <c r="D11">
+        <f>0.015*C11+0.03</f>
+        <v>0.18419999999999997</v>
+      </c>
       <c r="E11">
         <v>10.119999999999999</v>
       </c>
+      <c r="F11">
+        <f>0.01*E11+0.03</f>
+        <v>0.13119999999999998</v>
+      </c>
       <c r="G11">
         <v>14.38</v>
       </c>
+      <c r="H11">
+        <f>0.015*G11+0.03</f>
+        <v>0.2457</v>
+      </c>
       <c r="J11">
         <v>0.26960000000000001</v>
       </c>
+      <c r="K11">
+        <f t="shared" ref="K11:K12" si="7">0.01*J11+0.0003</f>
+        <v>2.996E-3</v>
+      </c>
       <c r="L11">
         <v>53.52</v>
       </c>
+      <c r="M11">
+        <f>0.015*L11+0.03</f>
+        <v>0.8328000000000001</v>
+      </c>
       <c r="N11">
-        <f>SQRT((J11/L11*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.493954483320445</v>
       </c>
     </row>
@@ -5343,23 +5530,47 @@
       <c r="A12">
         <v>8.6</v>
       </c>
+      <c r="B12">
+        <f t="shared" ref="B12:B14" si="8">0.01*A12+0.03</f>
+        <v>0.11599999999999999</v>
+      </c>
       <c r="C12">
         <v>8.59</v>
       </c>
+      <c r="D12">
+        <f t="shared" ref="D12:D16" si="9">0.015*C12+0.03</f>
+        <v>0.15884999999999999</v>
+      </c>
       <c r="E12">
         <v>8.66</v>
       </c>
+      <c r="F12">
+        <f t="shared" ref="F12:F14" si="10">0.01*E12+0.03</f>
+        <v>0.1166</v>
+      </c>
       <c r="G12">
         <v>12.22</v>
       </c>
+      <c r="H12">
+        <f t="shared" ref="H12:H16" si="11">0.015*G12+0.03</f>
+        <v>0.21329999999999999</v>
+      </c>
       <c r="J12">
         <v>0.12139999999999999</v>
       </c>
+      <c r="K12">
+        <f t="shared" si="7"/>
+        <v>1.5139999999999999E-3</v>
+      </c>
       <c r="L12">
         <v>24.12</v>
       </c>
+      <c r="M12">
+        <f>0.015*L12+0.03</f>
+        <v>0.39180000000000004</v>
+      </c>
       <c r="N12">
-        <f>SQRT((J12/L12*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="0"/>
         <v>13.478059291543516</v>
       </c>
     </row>
@@ -5367,46 +5578,94 @@
       <c r="A13">
         <v>7.02</v>
       </c>
+      <c r="B13">
+        <f t="shared" si="8"/>
+        <v>0.1002</v>
+      </c>
       <c r="C13">
         <v>6.98</v>
       </c>
+      <c r="D13">
+        <f t="shared" si="9"/>
+        <v>0.13469999999999999</v>
+      </c>
       <c r="E13">
         <v>6.99</v>
       </c>
+      <c r="F13">
+        <f t="shared" si="10"/>
+        <v>9.9900000000000003E-2</v>
+      </c>
       <c r="G13">
         <v>9.73</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="11"/>
+        <v>0.17595</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>5.65</v>
       </c>
+      <c r="B14">
+        <f t="shared" si="8"/>
+        <v>8.6499999999999994E-2</v>
+      </c>
       <c r="C14">
         <v>5.54</v>
       </c>
+      <c r="D14">
+        <f t="shared" si="9"/>
+        <v>0.11309999999999999</v>
+      </c>
       <c r="E14">
         <v>5.5620000000000003</v>
       </c>
+      <c r="F14">
+        <f t="shared" si="10"/>
+        <v>8.5620000000000002E-2</v>
+      </c>
       <c r="G14">
         <v>7.75</v>
       </c>
+      <c r="H14">
+        <f t="shared" si="11"/>
+        <v>0.14624999999999999</v>
+      </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>3.5539999999999998</v>
       </c>
+      <c r="B15">
+        <f>0.01*A15+0.003</f>
+        <v>3.8540000000000005E-2</v>
+      </c>
       <c r="C15">
         <v>3.46</v>
       </c>
+      <c r="D15">
+        <f t="shared" si="9"/>
+        <v>8.1900000000000001E-2</v>
+      </c>
       <c r="E15">
         <v>3.5750000000000002</v>
       </c>
+      <c r="F15">
+        <f>0.01*E15+0.003</f>
+        <v>3.8750000000000007E-2</v>
+      </c>
       <c r="G15">
         <v>4.92</v>
       </c>
+      <c r="H15">
+        <f t="shared" si="11"/>
+        <v>0.10379999999999999</v>
+      </c>
       <c r="J15" t="s">
         <v>2</v>
       </c>
@@ -5420,33 +5679,57 @@
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1.599</v>
       </c>
+      <c r="B16">
+        <f>0.01*A16+0.003</f>
+        <v>1.899E-2</v>
+      </c>
       <c r="C16">
         <v>1.52</v>
       </c>
+      <c r="D16">
+        <f t="shared" si="9"/>
+        <v>5.28E-2</v>
+      </c>
       <c r="E16">
         <v>1.6839999999999999</v>
       </c>
+      <c r="F16">
+        <f>0.01*E16+0.003</f>
+        <v>1.984E-2</v>
+      </c>
       <c r="G16">
         <v>2.2799999999999998</v>
       </c>
+      <c r="H16">
+        <f t="shared" si="11"/>
+        <v>6.4199999999999993E-2</v>
+      </c>
       <c r="J16">
         <v>5.5819999999999999</v>
       </c>
+      <c r="K16">
+        <f t="shared" ref="K16:K24" si="12">0.01*J16+0.003</f>
+        <v>5.8820000000000004E-2</v>
+      </c>
       <c r="L16">
         <v>250.6</v>
       </c>
+      <c r="M16">
+        <f t="shared" ref="M16:M23" si="13">0.015*L16+0.3</f>
+        <v>4.0590000000000002</v>
+      </c>
       <c r="N16">
-        <f>SQRT((J16/L16*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" ref="N16:N25" si="14">SQRT((J16/L16*1000)^2-$K$45^2)/$G$35*1000</f>
         <v>70.371062530501916</v>
       </c>
     </row>
@@ -5454,11 +5737,19 @@
       <c r="J17">
         <v>5.0679999999999996</v>
       </c>
+      <c r="K17">
+        <f t="shared" si="12"/>
+        <v>5.3679999999999999E-2</v>
+      </c>
       <c r="L17">
         <v>227.6</v>
       </c>
+      <c r="M17">
+        <f t="shared" si="13"/>
+        <v>3.7139999999999995</v>
+      </c>
       <c r="N17">
-        <f>SQRT((J17/L17*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>70.347311273893354</v>
       </c>
     </row>
@@ -5466,11 +5757,19 @@
       <c r="J18">
         <v>4.4509999999999996</v>
       </c>
+      <c r="K18">
+        <f t="shared" si="12"/>
+        <v>4.7509999999999997E-2</v>
+      </c>
       <c r="L18">
         <v>200.1</v>
       </c>
+      <c r="M18">
+        <f t="shared" si="13"/>
+        <v>3.3014999999999994</v>
+      </c>
       <c r="N18">
-        <f>SQRT((J18/L18*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>70.272721520985939</v>
       </c>
     </row>
@@ -5478,11 +5777,19 @@
       <c r="J19">
         <v>3.8809999999999998</v>
       </c>
+      <c r="K19">
+        <f t="shared" si="12"/>
+        <v>4.181E-2</v>
+      </c>
       <c r="L19">
         <v>174.8</v>
       </c>
+      <c r="M19">
+        <f t="shared" si="13"/>
+        <v>2.9219999999999997</v>
+      </c>
       <c r="N19">
-        <f>SQRT((J19/L19*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>70.14006759805639</v>
       </c>
     </row>
@@ -5490,11 +5797,19 @@
       <c r="J20">
         <v>3.302</v>
       </c>
+      <c r="K20">
+        <f t="shared" si="12"/>
+        <v>3.6020000000000003E-2</v>
+      </c>
       <c r="L20">
         <v>149</v>
       </c>
+      <c r="M20">
+        <f t="shared" si="13"/>
+        <v>2.5349999999999997</v>
+      </c>
       <c r="N20">
-        <f>SQRT((J20/L20*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>70.007145496431107</v>
       </c>
     </row>
@@ -5502,11 +5817,19 @@
       <c r="J21">
         <v>2.778</v>
       </c>
+      <c r="K21">
+        <f t="shared" si="12"/>
+        <v>3.0779999999999998E-2</v>
+      </c>
       <c r="L21">
         <v>125.5</v>
       </c>
+      <c r="M21">
+        <f t="shared" si="13"/>
+        <v>2.1824999999999997</v>
+      </c>
       <c r="N21">
-        <f>SQRT((J21/L21*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>69.92498594645545</v>
       </c>
     </row>
@@ -5514,11 +5837,19 @@
       <c r="J22">
         <v>2.2090000000000001</v>
       </c>
+      <c r="K22">
+        <f t="shared" si="12"/>
+        <v>2.5090000000000001E-2</v>
+      </c>
       <c r="L22">
         <v>100</v>
       </c>
+      <c r="M22">
+        <f t="shared" si="13"/>
+        <v>1.8</v>
+      </c>
       <c r="N22">
-        <f>SQRT((J22/L22*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>69.779180024817521</v>
       </c>
     </row>
@@ -5526,11 +5857,19 @@
       <c r="J23">
         <v>1.6359999999999999</v>
       </c>
+      <c r="K23">
+        <f t="shared" si="12"/>
+        <v>1.9359999999999999E-2</v>
+      </c>
       <c r="L23">
         <v>74.2</v>
       </c>
+      <c r="M23">
+        <f t="shared" si="13"/>
+        <v>1.413</v>
+      </c>
       <c r="N23">
-        <f>SQRT((J23/L23*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>69.646121987106085</v>
       </c>
     </row>
@@ -5538,11 +5877,19 @@
       <c r="J24">
         <v>0.93400000000000005</v>
       </c>
+      <c r="K24">
+        <f t="shared" si="12"/>
+        <v>1.234E-2</v>
+      </c>
       <c r="L24">
         <v>42.34</v>
       </c>
+      <c r="M24">
+        <f>0.015*L24+0.03</f>
+        <v>0.66510000000000002</v>
+      </c>
       <c r="N24">
-        <f>SQRT((J24/L24*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>69.681407790551177</v>
       </c>
     </row>
@@ -5550,17 +5897,25 @@
       <c r="J25">
         <v>0.48249999999999998</v>
       </c>
+      <c r="K25">
+        <f>0.01*J25+0.0003</f>
+        <v>5.1250000000000002E-3</v>
+      </c>
       <c r="L25">
         <v>22.08</v>
       </c>
+      <c r="M25">
+        <f>0.015*L25+0.03</f>
+        <v>0.36119999999999997</v>
+      </c>
       <c r="N25">
-        <f>SQRT((J25/L25*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="14"/>
         <v>69.016864006683065</v>
       </c>
     </row>
     <row r="27" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="10:15" x14ac:dyDescent="0.3">
@@ -5577,21 +5932,29 @@
         <v>5</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="10:15" x14ac:dyDescent="0.3">
       <c r="J29">
         <v>118.1</v>
       </c>
+      <c r="K29">
+        <f>0.01*J29+0.3</f>
+        <v>1.4810000000000001</v>
+      </c>
       <c r="L29">
         <v>215.6</v>
       </c>
+      <c r="M29">
+        <f t="shared" ref="M29:M36" si="15">0.015*L29+0.3</f>
+        <v>3.5339999999999998</v>
+      </c>
       <c r="N29">
-        <f>SQRT((J29/L29*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" ref="N29:N42" si="16">SQRT((J29/L29*1000)^2-$K$45^2)/$G$35*1000</f>
         <v>1743.5961876027409</v>
       </c>
     </row>
@@ -5599,11 +5962,19 @@
       <c r="J30">
         <v>110.9</v>
       </c>
+      <c r="K30">
+        <f t="shared" ref="K30:K35" si="17">0.01*J30+0.3</f>
+        <v>1.409</v>
+      </c>
       <c r="L30">
         <v>192.3</v>
       </c>
+      <c r="M30">
+        <f t="shared" si="15"/>
+        <v>3.1844999999999999</v>
+      </c>
       <c r="N30">
-        <f>SQRT((J30/L30*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>1835.6824490816189</v>
       </c>
     </row>
@@ -5611,11 +5982,19 @@
       <c r="J31">
         <v>103.2</v>
       </c>
+      <c r="K31">
+        <f t="shared" si="17"/>
+        <v>1.3320000000000001</v>
+      </c>
       <c r="L31">
         <v>170.2</v>
       </c>
+      <c r="M31">
+        <f t="shared" si="15"/>
+        <v>2.8529999999999998</v>
+      </c>
       <c r="N31">
-        <f>SQRT((J31/L31*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>1930.0381625887642</v>
       </c>
     </row>
@@ -5623,11 +6002,19 @@
       <c r="J32">
         <v>94.6</v>
       </c>
+      <c r="K32">
+        <f t="shared" si="17"/>
+        <v>1.246</v>
+      </c>
       <c r="L32">
         <v>148.30000000000001</v>
       </c>
+      <c r="M32">
+        <f t="shared" si="15"/>
+        <v>2.5244999999999997</v>
+      </c>
       <c r="N32">
-        <f>SQRT((J32/L32*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2030.4680592038183</v>
       </c>
     </row>
@@ -5635,11 +6022,19 @@
       <c r="J33">
         <v>85.2</v>
       </c>
+      <c r="K33">
+        <f t="shared" si="17"/>
+        <v>1.1520000000000001</v>
+      </c>
       <c r="L33">
         <v>126.5</v>
       </c>
+      <c r="M33">
+        <f t="shared" si="15"/>
+        <v>2.1974999999999998</v>
+      </c>
       <c r="N33">
-        <f>SQRT((J33/L33*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2143.8562066370696</v>
       </c>
     </row>
@@ -5649,25 +6044,33 @@
       </c>
       <c r="B34" s="1"/>
       <c r="C34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" t="s">
         <v>15</v>
       </c>
-      <c r="D34" t="s">
-        <v>16</v>
-      </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J34">
         <v>73.599999999999994</v>
       </c>
+      <c r="K34">
+        <f t="shared" si="17"/>
+        <v>1.036</v>
+      </c>
       <c r="L34">
         <v>103.8</v>
       </c>
+      <c r="M34">
+        <f t="shared" si="15"/>
+        <v>1.857</v>
+      </c>
       <c r="N34">
-        <f>SQRT((J34/L34*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2256.9783378875045</v>
       </c>
     </row>
@@ -5692,11 +6095,19 @@
       <c r="J35">
         <v>60.6</v>
       </c>
+      <c r="K35">
+        <f t="shared" si="17"/>
+        <v>0.90599999999999992</v>
+      </c>
       <c r="L35">
         <v>82</v>
       </c>
+      <c r="M35">
+        <f t="shared" si="15"/>
+        <v>1.53</v>
+      </c>
       <c r="N35">
-        <f>SQRT((J35/L35*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2352.3717533129875</v>
       </c>
     </row>
@@ -5714,17 +6125,25 @@
       <c r="J36">
         <v>45.11</v>
       </c>
+      <c r="K36">
+        <f>0.01*J36+0.03</f>
+        <v>0.48109999999999997</v>
+      </c>
       <c r="L36">
         <v>60.5</v>
       </c>
+      <c r="M36">
+        <f t="shared" si="15"/>
+        <v>1.2075</v>
+      </c>
       <c r="N36">
-        <f>SQRT((J36/L36*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2373.3658461550122</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37">
         <v>1.0244</v>
@@ -5736,17 +6155,25 @@
       <c r="J37">
         <v>35.130000000000003</v>
       </c>
+      <c r="K37">
+        <f t="shared" ref="K37:K39" si="18">0.01*J37+0.03</f>
+        <v>0.38130000000000008</v>
+      </c>
       <c r="L37">
         <v>48.18</v>
       </c>
+      <c r="M37">
+        <f>0.015*L37+0.03</f>
+        <v>0.75270000000000004</v>
+      </c>
       <c r="N37">
-        <f>SQRT((J37/L37*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2320.9108449293713</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>1.4327000000000001</v>
@@ -5758,11 +6185,19 @@
       <c r="J38">
         <v>23.69</v>
       </c>
+      <c r="K38">
+        <f t="shared" si="18"/>
+        <v>0.26690000000000003</v>
+      </c>
       <c r="L38">
         <v>35.56</v>
       </c>
+      <c r="M38">
+        <f t="shared" ref="M38:M42" si="19">0.015*L38+0.03</f>
+        <v>0.56340000000000001</v>
+      </c>
       <c r="N38">
-        <f>SQRT((J38/L38*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2120.5563313325829</v>
       </c>
     </row>
@@ -5770,11 +6205,19 @@
       <c r="J39">
         <v>10.56</v>
       </c>
+      <c r="K39">
+        <f t="shared" si="18"/>
+        <v>0.1356</v>
+      </c>
       <c r="L39">
         <v>21.19</v>
       </c>
+      <c r="M39">
+        <f t="shared" si="19"/>
+        <v>0.34784999999999999</v>
+      </c>
       <c r="N39">
-        <f>SQRT((J39/L39*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>1586.2681912429719</v>
       </c>
     </row>
@@ -5782,26 +6225,42 @@
       <c r="J40">
         <v>3.548</v>
       </c>
+      <c r="K40">
+        <f t="shared" ref="K40:K41" si="20">0.01*J40+0.003</f>
+        <v>3.8480000000000007E-2</v>
+      </c>
       <c r="L40">
         <v>10.71</v>
       </c>
+      <c r="M40">
+        <f t="shared" si="19"/>
+        <v>0.19065000000000001</v>
+      </c>
       <c r="N40">
-        <f>SQRT((J40/L40*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>1054.4588061879763</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J41">
         <v>1.1319999999999999</v>
       </c>
+      <c r="K41">
+        <f t="shared" si="20"/>
+        <v>1.4319999999999999E-2</v>
+      </c>
       <c r="L41">
         <v>4.7300000000000004</v>
       </c>
+      <c r="M41">
+        <f t="shared" si="19"/>
+        <v>0.10095</v>
+      </c>
       <c r="N41">
-        <f>SQRT((J41/L41*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>761.74101839229468</v>
       </c>
     </row>
@@ -5813,16 +6272,24 @@
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="J42">
         <v>53.48</v>
       </c>
+      <c r="K42">
+        <f>0.01*J42+0.03</f>
+        <v>0.56479999999999997</v>
+      </c>
       <c r="L42">
         <v>71.900000000000006</v>
       </c>
+      <c r="M42">
+        <f t="shared" ref="M42" si="21">0.015*L42+0.3</f>
+        <v>1.3785000000000001</v>
+      </c>
       <c r="N42">
-        <f>SQRT((J42/L42*1000)^2-$K$45^2)/$G$35*1000</f>
+        <f t="shared" si="16"/>
         <v>2367.6076254475088</v>
       </c>
     </row>
@@ -5834,24 +6301,38 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="D43">
-        <f>B43/C43*1000</f>
-        <v>4162000</v>
+        <f>B43/C43/1000</f>
+        <v>4.1619999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44">
+        <f>0.01*B43+0.03</f>
+        <v>0.23809999999999998</v>
+      </c>
+      <c r="C44">
+        <v>1E-4</v>
+      </c>
+      <c r="D44">
+        <f>D43*SQRT(SUMSQ(B44/B43,C44/C43))</f>
+        <v>9.5898706977727288E-2</v>
+      </c>
       <c r="J44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K45">
         <v>2.7210000000000001</v>

--- a/uloha7/uloha7.xlsx
+++ b/uloha7/uloha7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nemec\david\school\praktika\uloha7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{697A9A5B-5ECD-4822-A82F-4A84E72CC8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDBCF71A-67AE-454D-86E2-36BF09D965D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C78186FA-06F9-4A36-99E9-9DBABD2AC56F}"/>
   </bookViews>
@@ -6122,6 +6122,9 @@
         <f>C36/$G$35*1000</f>
         <v>1.3910142042126308</v>
       </c>
+      <c r="F36">
+        <v>5.0000000000000001E-3</v>
+      </c>
       <c r="J36">
         <v>45.11</v>
       </c>
